--- a/www/download/IND.surplus_value.empe_ls.r.pc.WIOD13.xlsx
+++ b/www/download/IND.surplus_value.empe_ls.r.pc.WIOD13.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>107.38</t>
+          <t>1.0740906751347</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>102.07</t>
+          <t>1.0209249070254</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>109.96</t>
+          <t>1.09978113708656</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>110.13</t>
+          <t>1.10126816146258</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>99.85</t>
+          <t>0.964251771606089</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>109.52</t>
+          <t>1.09535083228166</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>116.8</t>
+          <t>1.16839054580237</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>107.18</t>
+          <t>1.07217144524641</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.86</t>
+          <t>0.9487382880064</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>70.69</t>
+          <t>0.706976607232266</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>0.630127951847255</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>66.63</t>
+          <t>0.666356515834434</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>63.13</t>
+          <t>0.631554351623155</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>80.13</t>
+          <t>0.801265455463271</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>0.87773181251996</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>0.541593550602879</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>61.09</t>
+          <t>0.610840738484212</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>0.896193443143876</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>0.888676804643634</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>87.09</t>
+          <t>0.847534981339543</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>95.71</t>
+          <t>0.957183203738011</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>94.89</t>
+          <t>0.948811405729612</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>0.930444933138143</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>0.383234364922211</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>0.699247820131132</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>68.39</t>
+          <t>0.683892542027002</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>68.37</t>
+          <t>0.683702229827612</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>79.83</t>
+          <t>0.798714489020917</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>0.965095293963422</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>111.9</t>
+          <t>1.1190524389081</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-0.0938474873793222</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-10.9</t>
+          <t>-0.108960960536042</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-0.063536502922251</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-5.48</t>
+          <t>-0.0548668784583264</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-0.155528103544503</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-14.5</t>
+          <t>-0.144824082401787</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-19.02</t>
+          <t>-0.190060345599167</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>-0.256729731016777</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-46.35</t>
+          <t>-0.463480532927886</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-41.09</t>
+          <t>-0.410863865777853</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-39.59</t>
+          <t>-0.395893770555358</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-38.34</t>
+          <t>-0.383341072102482</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-0.323560775473188</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-24.79</t>
+          <t>-0.247877674805566</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-28.69</t>
+          <t>-0.286884772952006</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>302.26</t>
+          <t>3.02286500157316</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>346.73</t>
+          <t>3.46743512196962</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>401.44</t>
+          <t>4.01450115523518</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>315.02</t>
+          <t>3.15011984496775</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>368.01</t>
+          <t>3.5834038394001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>398.3</t>
+          <t>3.98320027795936</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>391.99</t>
+          <t>3.9201513591953</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>419.86</t>
+          <t>4.19911649191902</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>351.48</t>
+          <t>3.51505514950967</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>4.5598516391553</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>477.95</t>
+          <t>4.77967988171849</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>502.67</t>
+          <t>5.0272354126764</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>475.66</t>
+          <t>4.75701081870618</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>464.37</t>
+          <t>4.643274739484</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>409.56</t>
+          <t>4.09570439243379</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>578.68</t>
+          <t>5.78746542562461</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>593.94</t>
+          <t>5.93990319182422</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>633.03</t>
+          <t>6.3307145767882</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>636.42</t>
+          <t>6.36422752032458</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>726.09</t>
+          <t>7.08464554207756</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>718.89</t>
+          <t>7.18930587337412</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>757.87</t>
+          <t>7.57953641241567</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>803.34</t>
+          <t>8.03444173980872</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>807.45</t>
+          <t>8.07478244245643</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>784.84</t>
+          <t>7.84821992958238</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>735.23</t>
+          <t>7.35258899562905</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>734.4</t>
+          <t>7.34465006149614</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>733.31</t>
+          <t>7.3340655394918</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>704.5</t>
+          <t>7.04523524802558</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>694.24</t>
+          <t>6.94281240320246</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>143.87</t>
+          <t>1.43929221719379</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>159.92</t>
+          <t>1.59960609605274</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>172.11</t>
+          <t>1.72153761208345</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>158.75</t>
+          <t>1.58757176312172</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>151.45</t>
+          <t>1.4643867516045</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>134.96</t>
+          <t>1.34975032027552</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>122.44</t>
+          <t>1.22502055483763</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>127.47</t>
+          <t>1.27535911809078</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>117.14</t>
+          <t>1.17161806518405</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>111.28</t>
+          <t>1.11285395377849</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>0.9751606630432</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>90.84</t>
+          <t>0.908520947553095</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>100.22</t>
+          <t>1.00249337339206</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>106.72</t>
+          <t>1.06735110737577</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>120.9</t>
+          <t>1.20916510638428</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-25.09</t>
+          <t>-0.250925227184531</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-21.8</t>
+          <t>-0.217945773106995</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-17.19</t>
+          <t>-0.17192242345769</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-11.02</t>
+          <t>-0.110187755856657</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-0.0454912241983799</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.13</t>
+          <t>0.0812847305540521</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>0.194973676615165</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>30.44</t>
+          <t>0.304440879382781</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>39.76</t>
+          <t>0.39757923576459</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>0.421532925963999</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>51.23</t>
+          <t>0.512313611174063</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>59.44</t>
+          <t>0.594416630553371</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>73.75</t>
+          <t>0.73759897720717</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>76.51</t>
+          <t>0.765021863335619</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>82.31</t>
+          <t>0.82312286592313</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>172.32</t>
+          <t>1.72354989834663</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>164.57</t>
+          <t>1.64593804664611</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>203.72</t>
+          <t>2.03737408385412</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>190.87</t>
+          <t>1.90868321718894</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>166.45</t>
+          <t>1.61646009087486</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>180.22</t>
+          <t>1.8024226058179</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>158.53</t>
+          <t>1.58566527430868</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>154.35</t>
+          <t>1.54386100099298</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>104.72</t>
+          <t>1.04741079377908</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>145.44</t>
+          <t>1.45433807708323</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>153.83</t>
+          <t>1.53832735913445</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>159.77</t>
+          <t>1.59780893732621</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>193.5</t>
+          <t>1.93527959465579</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>147.82</t>
+          <t>1.47818030458251</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>207.01</t>
+          <t>2.07021356319294</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>580.73</t>
+          <t>5.80945168629935</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>377.05</t>
+          <t>3.77055814136859</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>414.81</t>
+          <t>4.14819220859266</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>404.21</t>
+          <t>4.04202242669398</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>408.76</t>
+          <t>4.03680882957648</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>420.86</t>
+          <t>4.20876521352368</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>387.53</t>
+          <t>3.8754751920783</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>355.81</t>
+          <t>3.55875338527067</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>189.65</t>
+          <t>1.89672300483476</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>291.66</t>
+          <t>2.91649585515775</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>279.77</t>
+          <t>2.7977519437518</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>295.79</t>
+          <t>2.95802461018871</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>268.34</t>
+          <t>2.68383853573854</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>266.6</t>
+          <t>2.66614530699655</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>331.15</t>
+          <t>3.31155373902207</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>0.418113999005351</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>59.33</t>
+          <t>0.593006336608277</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.34</t>
+          <t>0.833168735132558</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>0.77774131176431</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>70.98</t>
+          <t>0.686159628294814</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>0.650411915783297</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.84</t>
+          <t>0.677650677276819</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.11</t>
+          <t>0.671965151794946</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>0.445603388494266</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>53.48</t>
+          <t>0.534142637793328</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>53.45</t>
+          <t>0.534191146537892</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>54.75</t>
+          <t>0.547649026681088</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>50.57</t>
+          <t>0.506527222397474</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>64.81</t>
+          <t>0.648135239754086</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>0.777867308830885</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9.58</t>
+          <t>0.0959098423997979</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.35</t>
+          <t>0.12359997426695</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>0.459260011548952</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>0.356096409415584</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>0.339199815418419</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>44.88</t>
+          <t>0.448840706200548</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40.42</t>
+          <t>0.4042664768995</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>0.349027647716327</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21.63</t>
+          <t>0.216398099910719</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>0.227755302417369</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>20.52</t>
+          <t>0.205210305767318</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>0.239821792156942</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>15.03</t>
+          <t>0.150455566833504</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>0.238856508693118</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>0.375310996936803</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>98.52</t>
+          <t>0.985566732132734</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>109.78</t>
+          <t>1.09805352598862</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>149.07</t>
+          <t>1.49090880035583</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>130.6</t>
+          <t>1.30585722563763</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>119.36</t>
+          <t>1.15904826417913</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>1.19529142280991</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>109.46</t>
+          <t>1.09478025895771</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>101.22</t>
+          <t>1.0124232784795</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>0.632451156182084</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>76.32</t>
+          <t>0.763233622315935</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>74.67</t>
+          <t>0.746750727278678</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>70.31</t>
+          <t>0.703142849969182</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>70.31</t>
+          <t>0.703170407498074</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>75.44</t>
+          <t>0.754466301087236</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>97.24</t>
+          <t>0.972451479477863</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>546.28</t>
+          <t>5.46372962840936</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>493.86</t>
+          <t>4.93949280445424</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>468.61</t>
+          <t>4.68652787648493</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>428.57</t>
+          <t>4.28583707573947</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>468.15</t>
+          <t>4.59389780311722</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>392.11</t>
+          <t>3.92192706560602</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>373.24</t>
+          <t>3.7339293960915</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>273.4</t>
+          <t>2.73460664373642</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>1.36382846157049</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>204.51</t>
+          <t>2.04648282228669</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>223.21</t>
+          <t>2.23227845379126</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>216.65</t>
+          <t>2.16712853883862</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>168.03</t>
+          <t>1.68057921287284</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>128.37</t>
+          <t>1.28385641988462</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>140.22</t>
+          <t>1.40236183698293</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>0.431442319246593</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>0.411033732210376</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>0.688225157530347</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>63.99</t>
+          <t>0.640814028843019</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>66.39</t>
+          <t>0.643786922738352</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>86.28</t>
+          <t>0.86469222742795</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>79.82</t>
+          <t>0.799594955013256</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>79.07</t>
+          <t>0.79159522193113</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>0.495197458928706</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>55.65</t>
+          <t>0.556590949864871</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>0.528462537236341</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>47.91</t>
+          <t>0.478862805701691</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>46.86</t>
+          <t>0.468869423677589</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>47.72</t>
+          <t>0.477254205115263</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>57.17</t>
+          <t>0.571760878311229</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>0.579896062673698</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>61.73</t>
+          <t>0.617385715025849</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>0.848071053189282</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>66.83</t>
+          <t>0.668286965401622</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>55.98</t>
+          <t>0.535089211037739</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>0.554212666740683</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>0.477014644269252</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>0.386962731585954</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>0.0592333585689897</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>0.23584579340764</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>0.22313582021481</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>24.17</t>
+          <t>0.241774160514577</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>0.296084775818537</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>0.345554633160099</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>0.459502070950813</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>94.59</t>
+          <t>0.946006519292477</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>93.98</t>
+          <t>0.939945925038883</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>113.27</t>
+          <t>1.13275618555328</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>101.12</t>
+          <t>1.01111674936171</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>89.66</t>
+          <t>0.867501962497405</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>83.01</t>
+          <t>0.830357701514389</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>0.736725711140876</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>67.28</t>
+          <t>0.673076728656385</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>0.571185089012112</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>48.54</t>
+          <t>0.485400786992551</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>0.485074043347859</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>48.51</t>
+          <t>0.485132168244663</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>52.11</t>
+          <t>0.521240475642372</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>0.716903101041263</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>85.01</t>
+          <t>0.850162084090448</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>189.6</t>
+          <t>1.89609723464851</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>183.43</t>
+          <t>1.83434882442144</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>203.63</t>
+          <t>2.03635955136616</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>215.35</t>
+          <t>2.1534335734563</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>206.48</t>
+          <t>2.03911413682023</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>200.35</t>
+          <t>2.00360534634384</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>219.44</t>
+          <t>2.19472735506837</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>179.13</t>
+          <t>1.7917507103206</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>142.31</t>
+          <t>1.4232902673111</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>174.38</t>
+          <t>1.74396334378357</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>180.51</t>
+          <t>1.80474078185421</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>168.5</t>
+          <t>1.68513511869383</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>159.01</t>
+          <t>1.59034755894409</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>152.53</t>
+          <t>1.52563972121669</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>149.85</t>
+          <t>1.49864954800023</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>284.73</t>
+          <t>2.84803657464667</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>306.97</t>
+          <t>3.07029563269819</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>336.48</t>
+          <t>3.3652530634083</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>350.83</t>
+          <t>3.50825578029448</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>360.39</t>
+          <t>3.4877824579158</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>346.08</t>
+          <t>3.46132807931294</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>361.06</t>
+          <t>3.61136711851426</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>328.64</t>
+          <t>3.28749444604875</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>158.15</t>
+          <t>1.58189356088531</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>381.27</t>
+          <t>3.81248175861679</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>390.29</t>
+          <t>3.90326564336474</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>423.44</t>
+          <t>4.23507558772805</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>400.21</t>
+          <t>4.00300980477669</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>474.36</t>
+          <t>4.7439083541215</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>525.46</t>
+          <t>5.25478605750222</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>149.08</t>
+          <t>1.49085595791831</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>144.12</t>
+          <t>1.44124630330838</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>187.74</t>
+          <t>1.87747722286476</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>183.88</t>
+          <t>1.83881945626309</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>178.55</t>
+          <t>1.770681589781</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>173.27</t>
+          <t>1.73268678616685</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>182.68</t>
+          <t>1.82683674408941</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>187.58</t>
+          <t>1.87587030337796</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>162.2</t>
+          <t>1.62197367186449</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>183.02</t>
+          <t>1.83016888689036</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>170.59</t>
+          <t>1.70594889970318</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>154.43</t>
+          <t>1.54437136114429</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>145.6</t>
+          <t>1.4560385153017</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>149.98</t>
+          <t>1.49981966809224</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>138.69</t>
+          <t>1.38690453878885</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>1.38508924286584</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>1.63009123065858</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>155.8</t>
+          <t>1.55805843413234</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>170.73</t>
+          <t>1.7073121152533</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>182.24</t>
+          <t>1.79843904405626</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>197.16</t>
+          <t>1.97169158308277</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>195.49</t>
+          <t>1.95502844811333</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>202.14</t>
+          <t>2.02155598056351</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>190.06</t>
+          <t>1.90063349330199</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>176.24</t>
+          <t>1.76244550241675</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>163.45</t>
+          <t>1.63452708688474</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>156.41</t>
+          <t>1.56416445033142</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>157.41</t>
+          <t>1.57414361537475</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>166.94</t>
+          <t>1.66936825513026</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>155.71</t>
+          <t>1.55714606876518</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>85.51</t>
+          <t>0.855734456474345</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>0.875338756698846</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>120.9</t>
+          <t>1.20926343718533</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>136.09</t>
+          <t>1.36097157441748</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>141.15</t>
+          <t>1.37631708400356</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>142.47</t>
+          <t>1.42513433090122</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>123.11</t>
+          <t>1.23146595471258</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>112.85</t>
+          <t>1.12880334307916</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>134.73</t>
+          <t>1.3475213469964</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>149.27</t>
+          <t>1.49275993510822</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>115.68</t>
+          <t>1.15700961555074</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>142.77</t>
+          <t>1.4277685414545</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>103.71</t>
+          <t>1.03740287416005</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>94.27</t>
+          <t>0.94276583940359</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>75.98</t>
+          <t>0.759837912799122</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>72.86</t>
+          <t>0.729074409023342</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>82.67</t>
+          <t>0.827347760055943</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>103.65</t>
+          <t>1.03702076375861</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>108.31</t>
+          <t>1.08287899097242</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>1.05611298270068</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>111.7</t>
+          <t>1.11731386371438</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>102.55</t>
+          <t>1.02547767039073</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>97.68</t>
+          <t>0.977377189304906</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>58.49</t>
+          <t>0.58508337871956</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>70.09</t>
+          <t>0.700840444072816</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>70.63</t>
+          <t>0.706317030281467</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>69.78</t>
+          <t>0.697959476879148</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>75.67</t>
+          <t>0.756945924234212</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>0.797844957610154</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>98.74</t>
+          <t>0.987447931366495</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>52.35</t>
+          <t>0.52431580281684</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>74.86</t>
+          <t>0.749098600839999</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>92.54</t>
+          <t>0.925882147945713</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>99.15</t>
+          <t>0.991556010801538</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>86.39</t>
+          <t>0.843301264855179</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>74.94</t>
+          <t>0.749240909175978</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>79.67</t>
+          <t>0.79778107694503</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>91.93</t>
+          <t>0.92035259876053</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>0.851205841681576</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>78.41</t>
+          <t>0.784934526134063</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>79.73</t>
+          <t>0.798148882652368</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>0.903759777294344</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>110.06</t>
+          <t>1.10098512237473</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>116.22</t>
+          <t>1.1624660593031</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>109.09</t>
+          <t>1.08962167843196</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>124.19</t>
+          <t>1.24215878967394</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>133.59</t>
+          <t>1.33612731149781</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>158.63</t>
+          <t>1.58661916004688</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>192.42</t>
+          <t>1.92416787136737</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>191.3</t>
+          <t>1.86016470879422</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>183.36</t>
+          <t>1.83392178615626</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>204.19</t>
+          <t>2.04273334221779</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>200.23</t>
+          <t>2.0031498832562</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>182.23</t>
+          <t>1.82261284417025</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>184.46</t>
+          <t>1.84476355518047</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>174.36</t>
+          <t>1.7438493304473</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>166.62</t>
+          <t>1.66638848917751</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>172.73</t>
+          <t>1.72768383786683</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>198.12</t>
+          <t>1.98089235479632</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>217.73</t>
+          <t>2.17731596148098</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>400.55</t>
+          <t>4.0050462258966</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>363.13</t>
+          <t>3.63092667790555</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>359.59</t>
+          <t>3.59627869682947</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>309.48</t>
+          <t>3.09493030222856</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>298.34</t>
+          <t>2.94181527825394</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>299.37</t>
+          <t>2.99371709450645</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>287.75</t>
+          <t>2.87807806494295</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>282.01</t>
+          <t>2.82056810006319</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>1.81950918509195</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>297.66</t>
+          <t>2.97642932979665</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>2.9007402808843</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>275.84</t>
+          <t>2.75916311958754</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>222.96</t>
+          <t>2.2298874791413</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>188.11</t>
+          <t>1.88108175420464</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>193.38</t>
+          <t>1.93383357465276</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>0.302652602394002</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>51.87</t>
+          <t>0.518742812993277</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>83.49</t>
+          <t>0.834991752129603</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>97.61</t>
+          <t>0.976062876970957</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>102.02</t>
+          <t>0.977178881764835</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>110.16</t>
+          <t>1.10204795335983</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>128.85</t>
+          <t>1.28851310877698</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>1.12151322770206</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>52.37</t>
+          <t>0.524065217998952</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>94.42</t>
+          <t>0.944059196342581</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>86.59</t>
+          <t>0.865898909328122</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>91.36</t>
+          <t>0.913710897943615</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>119.95</t>
+          <t>1.20014920364902</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>97.49</t>
+          <t>0.974962264806688</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>146.2</t>
+          <t>1.46214138018775</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>385.53</t>
+          <t>3.85608290488768</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>354.59</t>
+          <t>3.54641698108104</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>344.69</t>
+          <t>3.44718052383534</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>346.5</t>
+          <t>3.46500643907792</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>363.12</t>
+          <t>3.58084436657344</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>436.84</t>
+          <t>4.36899352277241</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>445.62</t>
+          <t>4.45710853759443</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>468.12</t>
+          <t>4.68196539692793</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>312.97</t>
+          <t>3.13005206883832</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>455.83</t>
+          <t>4.55830104970654</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>388.28</t>
+          <t>3.8831658040836</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>341.51</t>
+          <t>3.41577994097319</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>290.31</t>
+          <t>2.90356897969463</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>249.07</t>
+          <t>2.4902321086695</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>327.98</t>
+          <t>3.27983393458009</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>806.76</t>
+          <t>8.06815133014493</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>891.34</t>
+          <t>8.91385369798352</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>960.81</t>
+          <t>9.60876707194281</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>893.6</t>
+          <t>8.9359115489002</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>840.03</t>
+          <t>8.20924859328072</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>814.29</t>
+          <t>8.14320795422676</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>741.92</t>
+          <t>7.42092975123592</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>761.99</t>
+          <t>7.62174723109084</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>791.82</t>
+          <t>7.91876611200073</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>830.4</t>
+          <t>8.30415943318074</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>820.21</t>
+          <t>8.20254139436969</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>906.95</t>
+          <t>9.07026459557847</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>958.09</t>
+          <t>9.58214070926166</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1028.18</t>
+          <t>10.2814434561788</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1029.68</t>
+          <t>10.2971001638447</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>186.91</t>
+          <t>1.86954464021598</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>172.76</t>
+          <t>1.72797995272948</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>233.24</t>
+          <t>2.33267377613644</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>204.68</t>
+          <t>2.04663789535924</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>175.21</t>
+          <t>1.7025904262969</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>162.46</t>
+          <t>1.62492941685665</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>100.57</t>
+          <t>1.00589335056468</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>122.59</t>
+          <t>1.22626204246157</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>0.671574911142481</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>161.2</t>
+          <t>1.61195972188083</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>165.42</t>
+          <t>1.65426951847101</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>173.78</t>
+          <t>1.73795293359323</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>162.94</t>
+          <t>1.62980634052659</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>131.86</t>
+          <t>1.31864023256208</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>169.16</t>
+          <t>1.69168046385998</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-0.133218896853506</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>-0.0743452619538164</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>0.370558229523467</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>0.149656545337857</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>0.0991546387298419</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>17.26</t>
+          <t>0.172635768568583</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>0.0634235971016082</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-0.0226606819836596</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-16.43</t>
+          <t>-0.164255264472319</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.0242043345405787</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>0.063261085774978</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>0.0623113437756091</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>0.0555052399629425</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.00166983660646181</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0.0410090708978248</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>157.72</t>
+          <t>1.57738524332585</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>148.01</t>
+          <t>1.48024264798356</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>149.2</t>
+          <t>1.49209405202842</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>138.85</t>
+          <t>1.38852219839517</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>156.54</t>
+          <t>1.54434237481935</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>181.44</t>
+          <t>1.81455117391395</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>261.12</t>
+          <t>2.61153320262926</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>281.7</t>
+          <t>2.81741424956836</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>177.41</t>
+          <t>1.7742380399902</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>337.28</t>
+          <t>3.37270919225394</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>318.47</t>
+          <t>3.18489415949252</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>334.39</t>
+          <t>3.34437209712773</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>350.99</t>
+          <t>3.51044386700026</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>308.64</t>
+          <t>3.08654056105181</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>349.59</t>
+          <t>3.49595941316006</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>153.73</t>
+          <t>1.53749099382686</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>150.53</t>
+          <t>1.50546735182084</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>187.8</t>
+          <t>1.87810964216426</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>159.32</t>
+          <t>1.59314819776416</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>166.63</t>
+          <t>1.62849336964702</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>162.57</t>
+          <t>1.6258374248971</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>153.39</t>
+          <t>1.5340541187144</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>158.12</t>
+          <t>1.58149152335689</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>117.59</t>
+          <t>1.17602474529881</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>164.66</t>
+          <t>1.64658799232887</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>171.05</t>
+          <t>1.71059701445436</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>1.96013934883626</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>192.86</t>
+          <t>1.92885306993</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>183.34</t>
+          <t>1.83337294730619</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>241.86</t>
+          <t>2.41865921563049</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>178.43</t>
+          <t>1.78438275767087</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>184.39</t>
+          <t>1.84396269892741</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>220.8</t>
+          <t>2.20804436329515</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>148.34</t>
+          <t>1.48340086931967</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>164.91</t>
+          <t>1.63288333003187</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>124.52</t>
+          <t>1.24525649690655</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>104.91</t>
+          <t>1.04913255275747</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>174.78</t>
+          <t>1.74793102147507</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>136.55</t>
+          <t>1.36559488803569</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>235.29</t>
+          <t>2.35291275489897</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>191.65</t>
+          <t>1.91663870990645</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>214.15</t>
+          <t>2.14202524300663</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>195.14</t>
+          <t>1.95170760270574</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>174.31</t>
+          <t>1.74270927970021</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>213.82</t>
+          <t>2.1382147084258</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>276.39</t>
+          <t>2.7641282855624</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>253.8</t>
+          <t>2.53819117174514</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>294.38</t>
+          <t>2.94394608839754</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>315.16</t>
+          <t>3.15149861765111</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>326.36</t>
+          <t>3.23662030274257</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>288.12</t>
+          <t>2.8812847913034</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>314.38</t>
+          <t>3.14411169971254</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>290.77</t>
+          <t>2.90794445271427</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>265.91</t>
+          <t>2.65922426316388</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>264.79</t>
+          <t>2.64791034868071</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>249.69</t>
+          <t>2.4970069326218</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>255.45</t>
+          <t>2.55472511132703</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>225.23</t>
+          <t>2.25247274366503</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>186.76</t>
+          <t>1.86738336812705</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>191.6</t>
+          <t>1.91597782056947</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>637.59</t>
+          <t>6.37689102752339</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>594.16</t>
+          <t>5.94205672035172</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>620.9</t>
+          <t>6.20965895619192</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>607.47</t>
+          <t>6.07471699935462</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>659.43</t>
+          <t>6.47681001694971</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>683.82</t>
+          <t>6.83850502244453</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>656.22</t>
+          <t>6.56343245508931</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>637.36</t>
+          <t>6.37476899113027</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>291.11</t>
+          <t>2.91110030261733</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>435.03</t>
+          <t>4.35012675214195</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>460.5</t>
+          <t>4.6055825315563</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>433.33</t>
+          <t>4.33342997400684</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>340.19</t>
+          <t>3.40094947675601</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>277.93</t>
+          <t>2.77905888104577</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>204.35</t>
+          <t>2.04344523639337</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>135.55</t>
+          <t>1.35608670514556</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>143.05</t>
+          <t>1.4308422327525</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>177.51</t>
+          <t>1.7753963710705</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>162.33</t>
+          <t>1.6233179811056</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>173.83</t>
+          <t>1.6938293236992</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>172.65</t>
+          <t>1.72671220481783</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>158.32</t>
+          <t>1.5830010490122</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>153.95</t>
+          <t>1.5396717321614</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>1.3350183556468</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>149.81</t>
+          <t>1.49773244536136</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1.59971078719944</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>161.47</t>
+          <t>1.61469864859246</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>150.48</t>
+          <t>1.50527511363266</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>89.68</t>
+          <t>0.897036755126287</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>100.95</t>
+          <t>1.0096981686244</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>0.486105541404659</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>0.465254045534466</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>69.74</t>
+          <t>0.697667971837858</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>0.587362445267328</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>0.572105143614055</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>48.13</t>
+          <t>0.481543985976216</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>47.09</t>
+          <t>0.471169526914471</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>0.425062073023935</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0.2002129944534</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>25.67</t>
+          <t>0.256723095564587</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>21.62</t>
+          <t>0.216261278915212</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>0.217163467443321</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>14.04</t>
+          <t>0.140526252396155</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>29.72</t>
+          <t>0.297287894071314</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>50.13</t>
+          <t>0.501308210521502</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>262.03</t>
+          <t>2.62052436259092</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>232.87</t>
+          <t>2.32883060496891</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>221.8</t>
+          <t>2.21814622881728</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>215.12</t>
+          <t>2.15118584159796</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>209.77</t>
+          <t>2.04802187228262</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>256.56</t>
+          <t>2.56575694628586</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>296.53</t>
+          <t>2.96567599745721</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>344.19</t>
+          <t>3.44254185449182</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>333.13</t>
+          <t>3.33153863841004</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>300.56</t>
+          <t>3.00565538287986</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>328.31</t>
+          <t>3.28317669851157</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>354.55</t>
+          <t>3.54593532439435</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>353.8</t>
+          <t>3.53853482529599</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>170.14</t>
+          <t>1.70133553676695</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>207.69</t>
+          <t>2.07702836001866</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1.22036424040668</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>107.34</t>
+          <t>1.07360445761945</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>1.38300146386786</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>149.39</t>
+          <t>1.49387217384503</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>155.81</t>
+          <t>1.51325804772816</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>146.7</t>
+          <t>1.46722006563241</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>137.43</t>
+          <t>1.37498104691591</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>143.43</t>
+          <t>1.43501124064986</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>145.11</t>
+          <t>1.45140530246423</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>148.56</t>
+          <t>1.48572324573438</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>148.67</t>
+          <t>1.48694020460023</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>157.61</t>
+          <t>1.57605818455911</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>186.02</t>
+          <t>1.86055045883146</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>185.94</t>
+          <t>1.85951848679038</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>229.67</t>
+          <t>2.29664445697085</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>180.1</t>
+          <t>1.80200538260083</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>187.87</t>
+          <t>1.87939437651947</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>174.34</t>
+          <t>1.74416410968634</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>182.14</t>
+          <t>1.82146989660456</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>180.75</t>
+          <t>1.77831105956655</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>1.58036175547972</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>150.17</t>
+          <t>1.50239895448406</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>146.14</t>
+          <t>1.4621587748939</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>138.27</t>
+          <t>1.38290700467035</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>140.38</t>
+          <t>1.40396120439508</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>144.43</t>
+          <t>1.44412563050068</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>150.79</t>
+          <t>1.50784701110437</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>166.18</t>
+          <t>1.66235992695471</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>192.04</t>
+          <t>1.92003424165248</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>196.01</t>
+          <t>1.9600774759698</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>1.00208813586066</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>111.15</t>
+          <t>1.11155799744527</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>113.73</t>
+          <t>1.13732723167652</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>119.68</t>
+          <t>1.19681582989023</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>123.86</t>
+          <t>1.19723537391111</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>1.1669859659963</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>122.78</t>
+          <t>1.22787595767994</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>127.62</t>
+          <t>1.27625483265471</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>108.78</t>
+          <t>1.08787602055962</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>146.64</t>
+          <t>1.46637190864792</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>139.85</t>
+          <t>1.39856142158836</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>136.71</t>
+          <t>1.36715543020838</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>143.74</t>
+          <t>1.43748746095867</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>138.82</t>
+          <t>1.38811216277925</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>163.57</t>
+          <t>1.63575371713533</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>57.76</t>
+          <t>0.577623173979222</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>65.72</t>
+          <t>0.657207942501565</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>72.12</t>
+          <t>0.721253197758127</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>79.25</t>
+          <t>0.792466577278868</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>0.852822355068471</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>95.98</t>
+          <t>0.959817882601981</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>103.64</t>
+          <t>1.03644793089642</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>111.3</t>
+          <t>1.11313384164131</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>105.64</t>
+          <t>1.05642841425511</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>116.52</t>
+          <t>1.16516763821402</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>117.55</t>
+          <t>1.17547313526352</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>119.7</t>
+          <t>1.19704268791953</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>127.91</t>
+          <t>1.27920128682539</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>128.91</t>
+          <t>1.28906226140996</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>137.38</t>
+          <t>1.37378486542363</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
